--- a/services/ami/ami/template.xlsx
+++ b/services/ami/ami/template.xlsx
@@ -21,24 +21,117 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
-  <si>
-    <t xml:space="preserve">Shot code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Id</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="37">
+  <si>
+    <t xml:space="preserve">Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendor Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% Complete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Next Submission Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turnover Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Layout Blocking Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Layout Final Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anim Blocking Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anim Final Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FX Blocking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FX Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comp 1st Pass Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comp WIP Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proposed Creative Final Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final Delivery Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latest Version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weekly Report</t>
   </si>
   <si>
     <t xml:space="preserve">[[shot]]</t>
   </si>
   <si>
+    <t xml:space="preserve">{sg_shot_type}</t>
+  </si>
+  <si>
     <t xml:space="preserve">{code}</t>
   </si>
   <si>
-    <t xml:space="preserve">{id}</t>
+    <t xml:space="preserve">{sg_vzo_status}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{sg_shared_shot}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{sg__}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{sg_next_delivery}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{sg_turnover_date}</t>
   </si>
   <si>
     <t xml:space="preserve">[[end]]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model Blocking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rig Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lookdev Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Env Blocking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[[asset]]</t>
   </si>
 </sst>
 </file>
@@ -139,8 +232,19 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:U4"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="19.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="20.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="17.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="19.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="24.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="22.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="22.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="21.38"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -149,24 +253,96 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="0" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -185,9 +361,101 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
+  <dimension ref="A1:Q4"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.08"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="L1" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="P1" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q1" s="0" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/services/ami/ami/template.xlsx
+++ b/services/ami/ami/template.xlsx
@@ -8,8 +8,9 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Shots" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="Assets" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Overview" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Shots" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Assets" sheetId="3" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -21,7 +22,94 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="74">
+  <si>
+    <t xml:space="preserve">Huckleberry VFX Vendor Weekly Report </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendor:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RVX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{date}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For Week Ending: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">{week_ending}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OVERALL ASSET &amp; SHOT STATUS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Assets:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Shots: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Assets Turned over:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Shots Turned Over:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In Progress:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Awaiting Material:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Omits: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">On Hold:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pending Review:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final pending QC:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proposed Final:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finals: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBBs: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">WEEKLY SHOT STATUS UPDATES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Official Counts Received this week: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shots Omitted this week:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shots added this week:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shots submitted for Comp Finals this week: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finals received this week: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finals with Tech Fix Received this week:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBBs received this week: </t>
+  </si>
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -89,59 +177,84 @@
     <t xml:space="preserve">[[shot]]</t>
   </si>
   <si>
+    <t xml:space="preserve">{sg_asset_type}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{sg_client_shot_name}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{sg_vzo_status}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{sg_shared_shot}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{sg__}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{sg_next_delivery}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{sg_turnover_date}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{layout_sg_blocking}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{layout_due_date}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{animation_sg_blocking}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{animation_due_date}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{fx_sg_blocking}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{fx_due_date}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[[end]]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model Blocking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rig Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lookdev Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Env Blocking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[[asset]]</t>
+  </si>
+  <si>
     <t xml:space="preserve">{sg_shot_type}</t>
   </si>
   <si>
     <t xml:space="preserve">{code}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{sg_vzo_status}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{sg_shared_shot}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{sg__}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{sg_next_delivery}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{sg_turnover_date}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[[end]]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Model Blocking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Model Final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rig Final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lookdev Final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Env Blocking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asset Final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[[asset]]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -162,6 +275,11 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -206,12 +324,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -232,117 +358,457 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38.4"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E19" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="G19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:U4"/>
   <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="37.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="19.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="20.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="17.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="23.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="17.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="19.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="22.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="16.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="19.81"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="24.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="22.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="16.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="22.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="21.38"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
+      <c r="A1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="U1" s="0" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>21</v>
+      <c r="A2" s="2" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>23</v>
+      <c r="A3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>28</v>
+        <v>57</v>
+      </c>
+      <c r="I3" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="J3" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="K3" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="L3" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="M3" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>29</v>
+      <c r="A4" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -356,7 +822,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -370,89 +836,89 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>36</v>
+      <c r="A2" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>23</v>
+      <c r="A3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>29</v>
+      <c r="A4" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
